--- a/data/trans_bre/P57_AC_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P57_AC_R-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 8,5</t>
+          <t>-4,15; 8,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 11,81</t>
+          <t>-1,43; 11,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 5,98</t>
+          <t>-6,55; 6,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,24; 12,03</t>
+          <t>-10,81; 12,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 15,49</t>
+          <t>-6,75; 14,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 22,24</t>
+          <t>-2,34; 21,12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 8,35</t>
+          <t>-8,45; 8,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-21,06; 32,01</t>
+          <t>-21,32; 35,12</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 8,64</t>
+          <t>-2,38; 8,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,08; 12,22</t>
+          <t>1,1; 11,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 5,45</t>
+          <t>-3,27; 6,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-31,8; -1,67</t>
+          <t>-32,71; -1,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 14,26</t>
+          <t>-3,6; 13,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,59; 20,1</t>
+          <t>1,67; 19,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 7,33</t>
+          <t>-4,14; 8,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-50,92; -2,91</t>
+          <t>-51,45; -3,37</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 5,88</t>
+          <t>-3,93; 6,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,11; 11,2</t>
+          <t>0,85; 10,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 6,41</t>
+          <t>-3,2; 6,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 5,04</t>
+          <t>-6,61; 4,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 8,92</t>
+          <t>-5,63; 9,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,55; 17,04</t>
+          <t>1,18; 16,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 8,49</t>
+          <t>-3,96; 7,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-10,35; 8,89</t>
+          <t>-10,2; 8,32</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 4,72</t>
+          <t>-7,0; 4,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,76; 15,46</t>
+          <t>4,56; 15,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 6,9</t>
+          <t>-1,49; 7,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 42,39</t>
+          <t>-2,8; 41,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-8,77; 6,98</t>
+          <t>-9,53; 7,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,82; 23,56</t>
+          <t>6,75; 23,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 8,81</t>
+          <t>-1,77; 9,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 194,43</t>
+          <t>-4,34; 211,43</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 12,08</t>
+          <t>0,27; 12,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,74; 15,27</t>
+          <t>2,76; 15,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 7,85</t>
+          <t>-2,76; 7,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 7,85</t>
+          <t>-1,24; 8,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,01; 18,1</t>
+          <t>0,41; 19,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,06; 25,02</t>
+          <t>4,09; 26,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 10,11</t>
+          <t>-3,26; 9,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 12,16</t>
+          <t>-1,75; 13,16</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 7,09</t>
+          <t>-5,48; 7,18</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 9,57</t>
+          <t>-3,94; 9,74</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,2; 16,08</t>
+          <t>5,09; 16,25</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 4,75</t>
+          <t>-5,63; 4,72</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 9,49</t>
+          <t>-6,89; 9,65</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 13,89</t>
+          <t>-5,17; 14,04</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,39; 21,32</t>
+          <t>6,2; 21,97</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 7,53</t>
+          <t>-8,26; 7,5</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 8,98</t>
+          <t>-4,97; 9,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 9,65</t>
+          <t>-5,13; 8,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 8,73</t>
+          <t>-2,37; 9,18</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 9,24</t>
+          <t>-1,6; 8,86</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 11,96</t>
+          <t>-6,02; 12,51</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 13,64</t>
+          <t>-6,41; 12,81</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 10,77</t>
+          <t>-2,64; 11,32</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 13,6</t>
+          <t>-2,16; 13,18</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,64; 5,21</t>
+          <t>0,45; 5,05</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,53; 8,8</t>
+          <t>4,52; 8,92</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,17; 4,86</t>
+          <t>1,1; 5,1</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 16,63</t>
+          <t>-1,63; 19,23</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,92; 7,84</t>
+          <t>0,64; 7,51</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,72; 13,49</t>
+          <t>6,66; 13,62</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,49; 6,21</t>
+          <t>1,37; 6,56</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 37,78</t>
+          <t>-2,66; 44,02</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P57_AC_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P57_AC_R-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,17</t>
+          <t>2,01</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 8,13</t>
+          <t>-4,01; 7,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 11,34</t>
+          <t>-0,92; 11,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 6,19</t>
+          <t>-6,11; 5,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,81; 12,75</t>
+          <t>-8,21; 12,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 14,59</t>
+          <t>-6,45; 14,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 21,12</t>
+          <t>-1,56; 20,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,45; 8,56</t>
+          <t>-7,88; 8,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-21,32; 35,12</t>
+          <t>-15,74; 31,72</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-11,94</t>
+          <t>-4,32</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-20,25%</t>
+          <t>-7,14%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 8,07</t>
+          <t>-2,13; 7,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,1; 11,92</t>
+          <t>1,16; 12,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 6,23</t>
+          <t>-3,49; 6,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-32,71; -1,98</t>
+          <t>-11,33; 2,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 13,41</t>
+          <t>-3,28; 12,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,67; 19,86</t>
+          <t>1,9; 20,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 8,36</t>
+          <t>-4,41; 8,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-51,45; -3,37</t>
+          <t>-17,7; 4,63</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,7</t>
+          <t>-0,85</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-1,16%</t>
+          <t>-1,35%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 6,35</t>
+          <t>-4,12; 6,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,85; 10,95</t>
+          <t>1,1; 10,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 6,01</t>
+          <t>-3,14; 5,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 4,82</t>
+          <t>-6,27; 4,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 9,52</t>
+          <t>-5,77; 10,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,18; 16,74</t>
+          <t>1,64; 16,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 7,95</t>
+          <t>-3,9; 7,88</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-10,2; 8,32</t>
+          <t>-9,53; 6,95</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16,71</t>
+          <t>2,5</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 4,77</t>
+          <t>-6,97; 4,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,56; 15,1</t>
+          <t>4,7; 15,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 7,35</t>
+          <t>-1,28; 7,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 41,8</t>
+          <t>-2,86; 7,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-9,53; 7,1</t>
+          <t>-9,57; 7,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,75; 23,33</t>
+          <t>6,54; 22,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 9,5</t>
+          <t>-1,55; 9,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 211,43</t>
+          <t>-4,51; 11,99</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,41</t>
+          <t>3,21</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,27; 12,73</t>
+          <t>-0,06; 12,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,76; 15,97</t>
+          <t>2,99; 15,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 7,03</t>
+          <t>-2,28; 7,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 8,59</t>
+          <t>-1,09; 8,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,41; 19,13</t>
+          <t>-0,08; 18,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,09; 26,34</t>
+          <t>4,36; 26,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 9,0</t>
+          <t>-2,73; 10,22</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 13,16</t>
+          <t>-1,55; 12,75</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0,67</t>
+          <t>-0,45</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-1,01%</t>
+          <t>-0,68%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 7,18</t>
+          <t>-5,85; 7,42</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 9,74</t>
+          <t>-3,55; 10,2</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,09; 16,25</t>
+          <t>5,13; 16,47</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 4,72</t>
+          <t>-5,73; 5,36</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 9,65</t>
+          <t>-7,04; 10,33</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 14,04</t>
+          <t>-4,67; 14,18</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,2; 21,97</t>
+          <t>6,36; 22,41</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-8,26; 7,5</t>
+          <t>-8,25; 8,46</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,5</t>
+          <t>3,22</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 9,25</t>
+          <t>-4,44; 9,54</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 8,93</t>
+          <t>-5,48; 9,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 9,18</t>
+          <t>-2,7; 8,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 8,86</t>
+          <t>-1,8; 9,72</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 12,51</t>
+          <t>-5,28; 12,82</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 12,81</t>
+          <t>-6,8; 13,63</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 11,32</t>
+          <t>-3,04; 10,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 13,18</t>
+          <t>-2,37; 14,57</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4,23</t>
+          <t>1,42</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,45; 5,05</t>
+          <t>0,62; 5,18</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,52; 8,92</t>
+          <t>4,74; 9,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,1; 5,1</t>
+          <t>1,26; 4,93</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 19,23</t>
+          <t>-0,74; 4,07</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,64; 7,51</t>
+          <t>0,91; 7,74</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,66; 13,62</t>
+          <t>6,96; 13,68</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,37; 6,56</t>
+          <t>1,57; 6,35</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 44,02</t>
+          <t>-1,13; 6,71</t>
         </is>
       </c>
     </row>
